--- a/Result/profitability/3056.xlsx
+++ b/Result/profitability/3056.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9425</v>
+        <v>0.9537500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>19.71625</v>
+        <v>19.6475</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.31</v>
       </c>
       <c r="M3" t="n">
-        <v>0.92125</v>
+        <v>0.105</v>
       </c>
       <c r="N3" t="n">
-        <v>22.5275</v>
+        <v>21.485</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>-0.19</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08749999999999999</v>
+        <v>-0.10375</v>
       </c>
       <c r="N4" t="n">
-        <v>21.90625</v>
+        <v>20.97125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.27</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.06375</v>
+        <v>-0.07375000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>21.07875</v>
+        <v>21.2125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07125000000000001</v>
+        <v>-0.0725</v>
       </c>
       <c r="N6" t="n">
-        <v>22.54625</v>
+        <v>22.9425</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,16 +1264,16 @@
         <v>-0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.08</v>
+        <v>-0.08499999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>23.6325</v>
+        <v>22.9325</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.04</v>
+        <v>-0.0475</v>
       </c>
       <c r="N8" t="n">
-        <v>22.9375</v>
+        <v>22.8475</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9800,6 +9800,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3056</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>241</v>
+      </c>
+      <c r="D75" t="n">
+        <v>203</v>
+      </c>
+      <c r="E75" t="n">
+        <v>38</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-29</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-12.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>22</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.01625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.7199999999999989</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04382227632379787</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07308743169398912</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
